--- a/reports/excel/selenium-report.xlsx
+++ b/reports/excel/selenium-report.xlsx
@@ -7,15 +7,17 @@
     <sheet sheetId="1" name="Functional Testing" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Deployable Status" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Validation Test" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="UIUX Test" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Unit Testing" state="visible" r:id="rId8"/>
+    <sheet sheetId="4" name="Form Validation Testing" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Login &amp; Signup Testing" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="UIUX Test" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Unit Testing" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="354">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -50,7 +52,7 @@
     <t>Additional Remarks</t>
   </si>
   <si>
-    <t>TC_4061</t>
+    <t>TC_0567</t>
   </si>
   <si>
     <t>Functional Testing</t>
@@ -71,7 +73,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.061Z</t>
+    <t>2026-06-18T05:58:20.567Z</t>
   </si>
   <si>
     <t>N/A</t>
@@ -80,1217 +82,1004 @@
     <t/>
   </si>
   <si>
-    <t>TC_4065</t>
+    <t>TC_0569</t>
   </si>
   <si>
     <t>TC_AUTH_002: should validate invalid login</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.065Z</t>
-  </si>
-  <si>
-    <t>TC_4071</t>
+    <t>2026-06-18T05:58:20.569Z</t>
+  </si>
+  <si>
+    <t>TC_0570</t>
   </si>
   <si>
     <t>TC_AUTH_003: should validate empty credentials</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.071Z</t>
-  </si>
-  <si>
-    <t>TC_4073</t>
+    <t>2026-06-18T05:58:20.570Z</t>
+  </si>
+  <si>
+    <t>TC_0571</t>
   </si>
   <si>
     <t>TC_AUTH_004: should validate forgot password flow</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.073Z</t>
-  </si>
-  <si>
-    <t>TC_4075</t>
+    <t>2026-06-18T05:58:20.571Z</t>
+  </si>
+  <si>
+    <t>TC_0574</t>
   </si>
   <si>
     <t>TC_AUTH_005: should validate user registration</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.076Z</t>
-  </si>
-  <si>
-    <t>TC_4077</t>
+    <t>2026-06-18T05:58:20.574Z</t>
   </si>
   <si>
     <t>TC_AUTH_006: should handle duplicate account registration</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.077Z</t>
-  </si>
-  <si>
-    <t>TC_4079</t>
+    <t>2026-06-18T05:58:20.575Z</t>
+  </si>
+  <si>
+    <t>TC_0576</t>
   </si>
   <si>
     <t>TC_AUTH_007: should validate logout functionality</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.079Z</t>
-  </si>
-  <si>
-    <t>TC_4081</t>
+    <t>2026-06-18T05:58:20.576Z</t>
+  </si>
+  <si>
+    <t>TC_0577</t>
   </si>
   <si>
     <t>TC_AUTH_008: should handle session timeout</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.081Z</t>
-  </si>
-  <si>
-    <t>TC_4087</t>
+    <t>2026-06-18T05:58:20.577Z</t>
+  </si>
+  <si>
+    <t>TC_0579</t>
   </si>
   <si>
     <t>TC_AUTH_009: should validate login with unverified email</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.087Z</t>
-  </si>
-  <si>
-    <t>TC_4089</t>
+    <t>2026-06-18T05:58:20.579Z</t>
   </si>
   <si>
     <t>TC_AUTH_010: should validate login with suspended account</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.089Z</t>
-  </si>
-  <si>
-    <t>TC_4091</t>
+    <t>2026-06-18T05:58:20.580Z</t>
+  </si>
+  <si>
+    <t>TC_0580</t>
   </si>
   <si>
     <t>TC_AUTH_011: should validate password reset token expiration</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.091Z</t>
-  </si>
-  <si>
-    <t>TC_4093</t>
+    <t>TC_0581</t>
   </si>
   <si>
     <t>TC_AUTH_012: should validate remember me functionality</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.093Z</t>
-  </si>
-  <si>
-    <t>TC_4102</t>
+    <t>2026-06-18T05:58:20.581Z</t>
+  </si>
+  <si>
+    <t>TC_0583</t>
   </si>
   <si>
     <t>TC_CRUD_001: Create new record with valid data</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.102Z</t>
-  </si>
-  <si>
-    <t>TC_4103</t>
+    <t>2026-06-18T05:58:20.583Z</t>
   </si>
   <si>
     <t>TC_CRUD_002: Create new record with missing required fields</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.103Z</t>
-  </si>
-  <si>
-    <t>TC_4105</t>
+    <t>TC_0584</t>
   </si>
   <si>
     <t>TC_CRUD_003: Read existing record details</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.105Z</t>
-  </si>
-  <si>
-    <t>TC_4106</t>
+    <t>2026-06-18T05:58:20.584Z</t>
   </si>
   <si>
     <t>TC_CRUD_004: Read record list pagination</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.106Z</t>
-  </si>
-  <si>
-    <t>TC_4107</t>
+    <t>TC_0585</t>
   </si>
   <si>
     <t>TC_CRUD_005: Update record with valid data</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.107Z</t>
-  </si>
-  <si>
-    <t>TC_4109</t>
+    <t>2026-06-18T05:58:20.585Z</t>
+  </si>
+  <si>
+    <t>TC_0586</t>
   </si>
   <si>
     <t>TC_CRUD_006: Update record with invalid data</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.109Z</t>
-  </si>
-  <si>
-    <t>TC_4110</t>
+    <t>2026-06-18T05:58:20.586Z</t>
+  </si>
+  <si>
+    <t>TC_0587</t>
   </si>
   <si>
     <t>TC_CRUD_007: Delete existing record</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.110Z</t>
-  </si>
-  <si>
-    <t>TC_4112</t>
+    <t>2026-06-18T05:58:20.587Z</t>
+  </si>
+  <si>
+    <t>TC_0588</t>
   </si>
   <si>
     <t>TC_CRUD_008: Cancel delete operation</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.112Z</t>
-  </si>
-  <si>
-    <t>TC_4117</t>
+    <t>2026-06-18T05:58:20.588Z</t>
   </si>
   <si>
     <t>TC_CRUD_009: Confirmation dialogs on delete</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.117Z</t>
-  </si>
-  <si>
-    <t>TC_4119</t>
+    <t>TC_0589</t>
   </si>
   <si>
     <t>TC_CRUD_010: Data persistence validation after refresh</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.119Z</t>
-  </si>
-  <si>
-    <t>TC_4121</t>
+    <t>2026-06-18T05:58:20.589Z</t>
+  </si>
+  <si>
+    <t>TC_0590</t>
   </si>
   <si>
     <t>TC_CRUD_011: Create record with duplicate unique key</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.121Z</t>
-  </si>
-  <si>
-    <t>TC_4122</t>
+    <t>2026-06-18T05:58:20.590Z</t>
   </si>
   <si>
     <t>TC_CRUD_012: Read operation on non-existent record</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.122Z</t>
-  </si>
-  <si>
-    <t>TC_4123</t>
+    <t>TC_0591</t>
   </si>
   <si>
     <t>TC_CRUD_013: Bulk delete records</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.123Z</t>
-  </si>
-  <si>
-    <t>TC_4125</t>
+    <t>2026-06-18T05:58:20.591Z</t>
   </si>
   <si>
     <t>TC_CRUD_014: Bulk update records</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.125Z</t>
-  </si>
-  <si>
-    <t>TC_4127</t>
+    <t>TC_0592</t>
   </si>
   <si>
     <t>TC_CRUD_015: File upload during create</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.127Z</t>
-  </si>
-  <si>
-    <t>TC_4130</t>
+    <t>2026-06-18T05:58:20.592Z</t>
   </si>
   <si>
     <t>TC_CRUD_016: File download from read view</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.130Z</t>
-  </si>
-  <si>
-    <t>TC_4134</t>
+    <t>TC_0593</t>
   </si>
   <si>
     <t>TC_CRUD_017: Record state transition</t>
   </si>
   <si>
-    <t>2026-06-13T04:40:54.134Z</t>
+    <t>2026-06-18T05:58:20.593Z</t>
+  </si>
+  <si>
+    <t>TC_CRUD_018: Inline editing in list view</t>
+  </si>
+  <si>
+    <t>TC_0594</t>
+  </si>
+  <si>
+    <t>TC_CRUD_019: Sort records by column</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.594Z</t>
+  </si>
+  <si>
+    <t>TC_CRUD_020: Filter records by criteria</t>
+  </si>
+  <si>
+    <t>TC_0595</t>
+  </si>
+  <si>
+    <t>TC_DASH_001: Dashboard loading</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.595Z</t>
+  </si>
+  <si>
+    <t>TC_0596</t>
+  </si>
+  <si>
+    <t>TC_DASH_002: Data rendering on widgets</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.596Z</t>
+  </si>
+  <si>
+    <t>TC_0597</t>
+  </si>
+  <si>
+    <t>TC_DASH_003: Navigation cards clickability</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.597Z</t>
+  </si>
+  <si>
+    <t>TC_DASH_004: Widgets and metrics accuracy</t>
+  </si>
+  <si>
+    <t>TC_0598</t>
+  </si>
+  <si>
+    <t>TC_DASH_005: User profile access from dashboard</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.598Z</t>
+  </si>
+  <si>
+    <t>TC_DASH_006: Dashboard refresh behavior</t>
+  </si>
+  <si>
+    <t>TC_0599</t>
+  </si>
+  <si>
+    <t>TC_DASH_007: Sidebar toggle state persistence</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.599Z</t>
+  </si>
+  <si>
+    <t>TC_DASH_008: Notifications panel open/close</t>
+  </si>
+  <si>
+    <t>TC_0600</t>
+  </si>
+  <si>
+    <t>TC_DASH_009: Recent activity feed updates</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.600Z</t>
+  </si>
+  <si>
+    <t>TC_DASH_010: Quick action buttons functionality</t>
+  </si>
+  <si>
+    <t>TC_0601</t>
+  </si>
+  <si>
+    <t>TC_DASH_011: Data charts rendering</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.601Z</t>
+  </si>
+  <si>
+    <t>TC_DASH_012: Data charts tooltips</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.602Z</t>
+  </si>
+  <si>
+    <t>TC_0603</t>
+  </si>
+  <si>
+    <t>TC_DASH_013: Dashboard layout responsiveness</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.603Z</t>
+  </si>
+  <si>
+    <t>TC_DASH_014: Theme toggle effect on dashboard</t>
+  </si>
+  <si>
+    <t>TC_0604</t>
+  </si>
+  <si>
+    <t>TC_DASH_015: Loading spinners presence during data fetch</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:20.604Z</t>
+  </si>
+  <si>
+    <t>TC_2240</t>
+  </si>
+  <si>
+    <t>should load the homepage</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.240Z</t>
+  </si>
+  <si>
+    <t>TC_2286</t>
+  </si>
+  <si>
+    <t>TC_NAV_001: Main menu navigation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.286Z</t>
+  </si>
+  <si>
+    <t>TC_2288</t>
+  </si>
+  <si>
+    <t>TC_NAV_002: Breadcrumb verification</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.288Z</t>
+  </si>
+  <si>
+    <t>TC_NAV_003: Browser back button navigation</t>
+  </si>
+  <si>
+    <t>TC_2289</t>
+  </si>
+  <si>
+    <t>TC_NAV_004: Browser forward button navigation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.289Z</t>
+  </si>
+  <si>
+    <t>TC_NAV_005: Page refresh behavior</t>
+  </si>
+  <si>
+    <t>TC_2290</t>
+  </si>
+  <si>
+    <t>TC_NAV_006: External links open in new tab</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.290Z</t>
+  </si>
+  <si>
+    <t>TC_NAV_007: Internal anchor links navigation</t>
+  </si>
+  <si>
+    <t>TC_2291</t>
+  </si>
+  <si>
+    <t>TC_NAV_008: Sidebar collapse/expand navigation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.291Z</t>
+  </si>
+  <si>
+    <t>TC_NAV_009: Footer links navigation</t>
+  </si>
+  <si>
+    <t>TC_2292</t>
+  </si>
+  <si>
+    <t>TC_NAV_010: Tab navigation within pages</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.292Z</t>
+  </si>
+  <si>
+    <t>TC_2293</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_001: Basic search functionality</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.293Z</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_002: Search with no results</t>
+  </si>
+  <si>
+    <t>TC_2294</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_003: Search query persistence</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.294Z</t>
+  </si>
+  <si>
+    <t>TC_2295</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_004: Apply single filter</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.295Z</t>
+  </si>
+  <si>
+    <t>TC_2296</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_005: Apply multiple filters</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.296Z</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_006: Clear all filters</t>
+  </si>
+  <si>
+    <t>TC_2297</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_007: Sort by date ascending</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.297Z</t>
+  </si>
+  <si>
+    <t>TC_2298</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_008: Sort by date descending</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.298Z</t>
+  </si>
+  <si>
+    <t>TC_2299</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_009: Sort by alphabet</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.299Z</t>
+  </si>
+  <si>
+    <t>TC_2301</t>
+  </si>
+  <si>
+    <t>TC_SEARCH_010: Search highlighting in results</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.301Z</t>
+  </si>
+  <si>
+    <t>TC_7195</t>
+  </si>
+  <si>
+    <t>Deployable Status</t>
+  </si>
+  <si>
+    <t>TC_E2E_001: Complete Student Journey (Register -&gt; Login -&gt; All Modules)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"input[placeholder="John Doe"]"}
+  (Session info: chrome=149.0.7827.104)</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:27.195Z</t>
+  </si>
+  <si>
+    <t>C:\Users\dell\Desktop\pdd\WebApp\reports\screenshots\tc_e2e_001__complete_student_journey__register____login____all_modules__1781762307192.png</t>
+  </si>
+  <si>
+    <t>TC_1328</t>
+  </si>
+  <si>
+    <t>TC_E2E_002: Complete Admin Journey (Register -&gt; Login -&gt; Admin Dashboard)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.328Z</t>
+  </si>
+  <si>
+    <t>TC_2862</t>
+  </si>
+  <si>
+    <t>TC_SMOKE_001: Validate application startup</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.862Z</t>
   </si>
   <si>
     <t>TC_4135</t>
   </si>
   <si>
-    <t>TC_CRUD_018: Inline editing in list view</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.135Z</t>
+    <t>TC_SMOKE_002: Validate login page accessibility</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.135Z</t>
   </si>
   <si>
     <t>TC_4136</t>
   </si>
   <si>
-    <t>TC_CRUD_019: Sort records by column</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.136Z</t>
+    <t>TC_SMOKE_003: Validate dashboard access (unauthorized)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.136Z</t>
+  </si>
+  <si>
+    <t>TC_4137</t>
+  </si>
+  <si>
+    <t>TC_SMOKE_004: Validate primary business flow presence</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.137Z</t>
+  </si>
+  <si>
+    <t>TC_SMOKE_005: Validate 404 page for invalid route</t>
+  </si>
+  <si>
+    <t>TC_1329</t>
+  </si>
+  <si>
+    <t>Validation Test</t>
+  </si>
+  <si>
+    <t>TC_ERR_001: Invalid URL routing (404)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.329Z</t>
+  </si>
+  <si>
+    <t>TC_1330</t>
+  </si>
+  <si>
+    <t>TC_ERR_002: Server error rendering (500)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.330Z</t>
+  </si>
+  <si>
+    <t>TC_ERR_003: Network disconnection handling</t>
+  </si>
+  <si>
+    <t>TC_1331</t>
+  </si>
+  <si>
+    <t>TC_ERR_004: Graceful degradation on API failure</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.331Z</t>
+  </si>
+  <si>
+    <t>TC_ERR_005: Form submission timeout handling</t>
+  </si>
+  <si>
+    <t>TC_1332</t>
+  </si>
+  <si>
+    <t>TC_ERR_006: Invalid API response format handling</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.332Z</t>
+  </si>
+  <si>
+    <t>TC_1333</t>
+  </si>
+  <si>
+    <t>TC_ERR_007: Image loading failure fallback</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.333Z</t>
+  </si>
+  <si>
+    <t>TC_1336</t>
+  </si>
+  <si>
+    <t>TC_ERR_008: Unauthorized API call handling (401/403)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.336Z</t>
+  </si>
+  <si>
+    <t>TC_1337</t>
+  </si>
+  <si>
+    <t>TC_ERR_009: Rate limit exceeded handling (429)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.337Z</t>
+  </si>
+  <si>
+    <t>TC_1338</t>
+  </si>
+  <si>
+    <t>TC_ERR_010: Error boundary rendering in React/Vite</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.338Z</t>
+  </si>
+  <si>
+    <t>TC_1862</t>
+  </si>
+  <si>
+    <t>TC_FORM_001: Required field validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.862Z</t>
+  </si>
+  <si>
+    <t>TC_1863</t>
+  </si>
+  <si>
+    <t>TC_FORM_002: Invalid email format validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.863Z</t>
+  </si>
+  <si>
+    <t>TC_1864</t>
+  </si>
+  <si>
+    <t>TC_FORM_003: Boundary value testing for numbers</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.864Z</t>
+  </si>
+  <si>
+    <t>TC_FORM_004: Empty field handling on submit</t>
+  </si>
+  <si>
+    <t>TC_1865</t>
+  </si>
+  <si>
+    <t>TC_FORM_005: Maximum length checks</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.865Z</t>
+  </si>
+  <si>
+    <t>TC_1866</t>
+  </si>
+  <si>
+    <t>TC_FORM_006: Minimum length checks</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.866Z</t>
+  </si>
+  <si>
+    <t>TC_1871</t>
+  </si>
+  <si>
+    <t>TC_FORM_007: Numeric only validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.871Z</t>
+  </si>
+  <si>
+    <t>TC_1872</t>
+  </si>
+  <si>
+    <t>TC_FORM_008: Special character validation rejection</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.872Z</t>
+  </si>
+  <si>
+    <t>TC_1873</t>
+  </si>
+  <si>
+    <t>TC_FORM_009: Special character validation acceptance</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.873Z</t>
+  </si>
+  <si>
+    <t>TC_1874</t>
+  </si>
+  <si>
+    <t>TC_FORM_010: Form reset functionality</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.874Z</t>
+  </si>
+  <si>
+    <t>TC_FORM_011: Date picker format validation</t>
+  </si>
+  <si>
+    <t>TC_1875</t>
+  </si>
+  <si>
+    <t>TC_FORM_012: Future date validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.875Z</t>
+  </si>
+  <si>
+    <t>TC_1876</t>
+  </si>
+  <si>
+    <t>TC_FORM_013: Past date validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.876Z</t>
+  </si>
+  <si>
+    <t>TC_FORM_014: Dropdown selection validation</t>
+  </si>
+  <si>
+    <t>TC_1877</t>
+  </si>
+  <si>
+    <t>TC_FORM_015: Multi-select dropdown validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.877Z</t>
+  </si>
+  <si>
+    <t>TC_2303</t>
+  </si>
+  <si>
+    <t>TC_SEC_001: Session persistence on reload</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.303Z</t>
+  </si>
+  <si>
+    <t>TC_2304</t>
+  </si>
+  <si>
+    <t>TC_SEC_002: Unauthorized access prevention to dashboard</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.304Z</t>
+  </si>
+  <si>
+    <t>TC_2305</t>
+  </si>
+  <si>
+    <t>TC_SEC_003: Protected route redirection to login</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.305Z</t>
+  </si>
+  <si>
+    <t>TC_SEC_004: Logout invalidates session</t>
+  </si>
+  <si>
+    <t>TC_2306</t>
+  </si>
+  <si>
+    <t>TC_SEC_005: Role-based access control (Admin)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.306Z</t>
+  </si>
+  <si>
+    <t>TC_2307</t>
+  </si>
+  <si>
+    <t>TC_SEC_006: Role-based access control (User)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.307Z</t>
+  </si>
+  <si>
+    <t>TC_SEC_007: XSS injection prevention in forms</t>
+  </si>
+  <si>
+    <t>TC_2308</t>
+  </si>
+  <si>
+    <t>TC_SEC_008: SQL injection prevention in search</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.308Z</t>
+  </si>
+  <si>
+    <t>TC_2309</t>
+  </si>
+  <si>
+    <t>TC_SEC_009: CSRF token presence</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.309Z</t>
+  </si>
+  <si>
+    <t>TC_2310</t>
+  </si>
+  <si>
+    <t>TC_SEC_010: Secure cookie attributes</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.310Z</t>
+  </si>
+  <si>
+    <t>TC_1861</t>
+  </si>
+  <si>
+    <t>Form Validation Testing</t>
+  </si>
+  <si>
+    <t>should show error for empty form submission</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:41.861Z</t>
+  </si>
+  <si>
+    <t>TC_2282</t>
+  </si>
+  <si>
+    <t>Login &amp; Signup Testing</t>
+  </si>
+  <si>
+    <t>should navigate to login page</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:42.282Z</t>
   </si>
   <si>
     <t>TC_4138</t>
   </si>
   <si>
-    <t>TC_CRUD_020: Filter records by criteria</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.138Z</t>
+    <t>UI/UX Test</t>
+  </si>
+  <si>
+    <t>TC_UI_001: Core element visibility on load</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.138Z</t>
+  </si>
+  <si>
+    <t>TC_4139</t>
+  </si>
+  <si>
+    <t>TC_UI_002: Button alignment and spacing</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.139Z</t>
+  </si>
+  <si>
+    <t>TC_UI_003: Form layout consistency</t>
+  </si>
+  <si>
+    <t>TC_4140</t>
+  </si>
+  <si>
+    <t>TC_UI_004: Responsive layout checks (Mobile viewport)</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.140Z</t>
+  </si>
+  <si>
+    <t>TC_UI_005: Responsive layout checks (Tablet viewport)</t>
+  </si>
+  <si>
+    <t>TC_4141</t>
+  </si>
+  <si>
+    <t>TC_UI_006: Navigation menu usability</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.141Z</t>
+  </si>
+  <si>
+    <t>TC_UI_007: Broken link detection across major pages</t>
   </si>
   <si>
     <t>TC_4142</t>
   </si>
   <si>
-    <t>TC_DASH_001: Dashboard loading</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.142Z</t>
+    <t>TC_UI_008: Image loading and resolution verification</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.142Z</t>
+  </si>
+  <si>
+    <t>TC_UI_009: Font family and typography consistency</t>
   </si>
   <si>
     <t>TC_4143</t>
   </si>
   <si>
-    <t>TC_DASH_002: Data rendering on widgets</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.143Z</t>
+    <t>TC_UI_010: Color palette and contrast accessibility</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.143Z</t>
+  </si>
+  <si>
+    <t>TC_4144</t>
+  </si>
+  <si>
+    <t>Unit Testing</t>
+  </si>
+  <si>
+    <t>TC_UNIT_001: Validate password hashing utility logic</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.144Z</t>
+  </si>
+  <si>
+    <t>TC_UNIT_002: Validate email regex format utility</t>
+  </si>
+  <si>
+    <t>TC_UNIT_003: Validate URL parsing utility</t>
+  </si>
+  <si>
+    <t>TC_4145</t>
+  </si>
+  <si>
+    <t>TC_UNIT_004: Validate date formatting helper</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.145Z</t>
+  </si>
+  <si>
+    <t>TC_UNIT_005: Verify number currency formatting helper</t>
+  </si>
+  <si>
+    <t>TC_4146</t>
+  </si>
+  <si>
+    <t>TC_UNIT_006: Check application state reducer for login</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:58:44.146Z</t>
+  </si>
+  <si>
+    <t>TC_UNIT_007: Check application state reducer for logout</t>
   </si>
   <si>
     <t>TC_4147</t>
   </si>
   <si>
-    <t>TC_DASH_003: Navigation cards clickability</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.147Z</t>
-  </si>
-  <si>
-    <t>TC_4150</t>
-  </si>
-  <si>
-    <t>TC_DASH_004: Widgets and metrics accuracy</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.150Z</t>
-  </si>
-  <si>
-    <t>TC_4151</t>
-  </si>
-  <si>
-    <t>TC_DASH_005: User profile access from dashboard</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.151Z</t>
-  </si>
-  <si>
-    <t>TC_4153</t>
-  </si>
-  <si>
-    <t>TC_DASH_006: Dashboard refresh behavior</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.153Z</t>
-  </si>
-  <si>
-    <t>TC_4154</t>
-  </si>
-  <si>
-    <t>TC_DASH_007: Sidebar toggle state persistence</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.154Z</t>
-  </si>
-  <si>
-    <t>TC_4155</t>
-  </si>
-  <si>
-    <t>TC_DASH_008: Notifications panel open/close</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.155Z</t>
-  </si>
-  <si>
-    <t>TC_4157</t>
-  </si>
-  <si>
-    <t>TC_DASH_009: Recent activity feed updates</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.157Z</t>
-  </si>
-  <si>
-    <t>TC_4159</t>
-  </si>
-  <si>
-    <t>TC_DASH_010: Quick action buttons functionality</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.159Z</t>
-  </si>
-  <si>
-    <t>TC_4163</t>
-  </si>
-  <si>
-    <t>TC_DASH_011: Data charts rendering</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.163Z</t>
-  </si>
-  <si>
-    <t>TC_4167</t>
-  </si>
-  <si>
-    <t>TC_DASH_012: Data charts tooltips</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.167Z</t>
-  </si>
-  <si>
-    <t>TC_DASH_013: Dashboard layout responsiveness</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.168Z</t>
-  </si>
-  <si>
-    <t>TC_4169</t>
-  </si>
-  <si>
-    <t>TC_DASH_014: Theme toggle effect on dashboard</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.169Z</t>
-  </si>
-  <si>
-    <t>TC_4170</t>
-  </si>
-  <si>
-    <t>TC_DASH_015: Loading spinners presence during data fetch</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:54.170Z</t>
-  </si>
-  <si>
-    <t>TC_3887</t>
-  </si>
-  <si>
-    <t>TC_NAV_001: Main menu navigation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.888Z</t>
-  </si>
-  <si>
-    <t>TC_3895</t>
-  </si>
-  <si>
-    <t>TC_NAV_002: Breadcrumb verification</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.895Z</t>
-  </si>
-  <si>
-    <t>TC_3904</t>
-  </si>
-  <si>
-    <t>TC_NAV_003: Browser back button navigation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.904Z</t>
-  </si>
-  <si>
-    <t>TC_3907</t>
-  </si>
-  <si>
-    <t>TC_NAV_004: Browser forward button navigation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.907Z</t>
-  </si>
-  <si>
-    <t>TC_3911</t>
-  </si>
-  <si>
-    <t>TC_NAV_005: Page refresh behavior</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.911Z</t>
-  </si>
-  <si>
-    <t>TC_3918</t>
-  </si>
-  <si>
-    <t>TC_NAV_006: External links open in new tab</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.918Z</t>
-  </si>
-  <si>
-    <t>TC_3923</t>
-  </si>
-  <si>
-    <t>TC_NAV_007: Internal anchor links navigation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.923Z</t>
-  </si>
-  <si>
-    <t>TC_3927</t>
-  </si>
-  <si>
-    <t>TC_NAV_008: Sidebar collapse/expand navigation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.927Z</t>
-  </si>
-  <si>
-    <t>TC_3936</t>
-  </si>
-  <si>
-    <t>TC_NAV_009: Footer links navigation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.936Z</t>
-  </si>
-  <si>
-    <t>TC_3940</t>
-  </si>
-  <si>
-    <t>TC_NAV_010: Tab navigation within pages</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.940Z</t>
-  </si>
-  <si>
-    <t>TC_3956</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_001: Basic search functionality</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.956Z</t>
-  </si>
-  <si>
-    <t>TC_3959</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_002: Search with no results</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.959Z</t>
-  </si>
-  <si>
-    <t>TC_3968</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_003: Search query persistence</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.968Z</t>
-  </si>
-  <si>
-    <t>TC_3973</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_004: Apply single filter</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.973Z</t>
-  </si>
-  <si>
-    <t>TC_3975</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_005: Apply multiple filters</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.975Z</t>
-  </si>
-  <si>
-    <t>TC_3979</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_006: Clear all filters</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.979Z</t>
-  </si>
-  <si>
-    <t>TC_3989</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_007: Sort by date ascending</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.989Z</t>
-  </si>
-  <si>
-    <t>TC_3993</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_008: Sort by date descending</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.993Z</t>
-  </si>
-  <si>
-    <t>TC_3997</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_009: Sort by alphabet</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.997Z</t>
-  </si>
-  <si>
-    <t>TC_4006</t>
-  </si>
-  <si>
-    <t>TC_SEARCH_010: Search highlighting in results</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.006Z</t>
-  </si>
-  <si>
-    <t>TC_8370</t>
-  </si>
-  <si>
-    <t>Deployable Status</t>
-  </si>
-  <si>
-    <t>TC_E2E_001: Complete Student Journey (Register -&gt; Login -&gt; All Modules)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"input[placeholder="John Doe"]"}
-  (Session info: chrome=148.0.7778.217)</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:40:58.370Z</t>
-  </si>
-  <si>
-    <t>C:\Users\dell\Desktop\PDD-Web App\WebApp\reports\screenshots\tc_e2e_001__complete_student_journey__register____login____all_modules__1781325658361.png</t>
-  </si>
-  <si>
-    <t>TC_3692</t>
-  </si>
-  <si>
-    <t>TC_E2E_002: Complete Admin Journey (Register -&gt; Login -&gt; Admin Dashboard)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.692Z</t>
-  </si>
-  <si>
-    <t>TC_4420</t>
-  </si>
-  <si>
-    <t>TC_SMOKE_001: Validate application startup</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.420Z</t>
-  </si>
-  <si>
-    <t>TC_5673</t>
-  </si>
-  <si>
-    <t>TC_SMOKE_002: Validate login page accessibility</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.673Z</t>
-  </si>
-  <si>
-    <t>TC_5679</t>
-  </si>
-  <si>
-    <t>TC_SMOKE_003: Validate dashboard access (unauthorized)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.679Z</t>
-  </si>
-  <si>
-    <t>TC_5695</t>
-  </si>
-  <si>
-    <t>TC_SMOKE_004: Validate primary business flow presence</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.695Z</t>
-  </si>
-  <si>
-    <t>TC_5703</t>
-  </si>
-  <si>
-    <t>TC_SMOKE_005: Validate 404 page for invalid route</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.703Z</t>
-  </si>
-  <si>
-    <t>TC_3721</t>
-  </si>
-  <si>
-    <t>Validation Test</t>
-  </si>
-  <si>
-    <t>TC_ERR_001: Invalid URL routing (404)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.721Z</t>
-  </si>
-  <si>
-    <t>TC_3728</t>
-  </si>
-  <si>
-    <t>TC_ERR_002: Server error rendering (500)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.728Z</t>
-  </si>
-  <si>
-    <t>TC_3737</t>
-  </si>
-  <si>
-    <t>TC_ERR_003: Network disconnection handling</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.737Z</t>
-  </si>
-  <si>
-    <t>TC_3741</t>
-  </si>
-  <si>
-    <t>TC_ERR_004: Graceful degradation on API failure</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.741Z</t>
-  </si>
-  <si>
-    <t>TC_3745</t>
-  </si>
-  <si>
-    <t>TC_ERR_005: Form submission timeout handling</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.745Z</t>
-  </si>
-  <si>
-    <t>TC_3754</t>
-  </si>
-  <si>
-    <t>TC_ERR_006: Invalid API response format handling</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.754Z</t>
-  </si>
-  <si>
-    <t>TC_3757</t>
-  </si>
-  <si>
-    <t>TC_ERR_007: Image loading failure fallback</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.757Z</t>
-  </si>
-  <si>
-    <t>TC_3762</t>
-  </si>
-  <si>
-    <t>TC_ERR_008: Unauthorized API call handling (401/403)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.762Z</t>
-  </si>
-  <si>
-    <t>TC_3769</t>
-  </si>
-  <si>
-    <t>TC_ERR_009: Rate limit exceeded handling (429)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.769Z</t>
-  </si>
-  <si>
-    <t>TC_3774</t>
-  </si>
-  <si>
-    <t>TC_ERR_010: Error boundary rendering in React/Vite</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.774Z</t>
-  </si>
-  <si>
-    <t>TC_3788</t>
-  </si>
-  <si>
-    <t>TC_FORM_001: Required field validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.788Z</t>
-  </si>
-  <si>
-    <t>TC_3793</t>
-  </si>
-  <si>
-    <t>TC_FORM_002: Invalid email format validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.793Z</t>
-  </si>
-  <si>
-    <t>TC_3800</t>
-  </si>
-  <si>
-    <t>TC_FORM_003: Boundary value testing for numbers</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.800Z</t>
-  </si>
-  <si>
-    <t>TC_3807</t>
-  </si>
-  <si>
-    <t>TC_FORM_004: Empty field handling on submit</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.807Z</t>
-  </si>
-  <si>
-    <t>TC_3811</t>
-  </si>
-  <si>
-    <t>TC_FORM_005: Maximum length checks</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.811Z</t>
-  </si>
-  <si>
-    <t>TC_3819</t>
-  </si>
-  <si>
-    <t>TC_FORM_006: Minimum length checks</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.819Z</t>
-  </si>
-  <si>
-    <t>TC_3823</t>
-  </si>
-  <si>
-    <t>TC_FORM_007: Numeric only validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.823Z</t>
-  </si>
-  <si>
-    <t>TC_3827</t>
-  </si>
-  <si>
-    <t>TC_FORM_008: Special character validation rejection</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.827Z</t>
-  </si>
-  <si>
-    <t>TC_3837</t>
-  </si>
-  <si>
-    <t>TC_FORM_009: Special character validation acceptance</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.837Z</t>
-  </si>
-  <si>
-    <t>TC_3841</t>
-  </si>
-  <si>
-    <t>TC_FORM_010: Form reset functionality</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.841Z</t>
-  </si>
-  <si>
-    <t>TC_3852</t>
-  </si>
-  <si>
-    <t>TC_FORM_011: Date picker format validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.852Z</t>
-  </si>
-  <si>
-    <t>TC_3855</t>
-  </si>
-  <si>
-    <t>TC_FORM_012: Future date validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.855Z</t>
-  </si>
-  <si>
-    <t>TC_3859</t>
-  </si>
-  <si>
-    <t>TC_FORM_013: Past date validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.859Z</t>
-  </si>
-  <si>
-    <t>TC_3868</t>
-  </si>
-  <si>
-    <t>TC_FORM_014: Dropdown selection validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.868Z</t>
-  </si>
-  <si>
-    <t>TC_3872</t>
-  </si>
-  <si>
-    <t>TC_FORM_015: Multi-select dropdown validation</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:13.872Z</t>
-  </si>
-  <si>
-    <t>TC_4021</t>
-  </si>
-  <si>
-    <t>TC_SEC_001: Session persistence on reload</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.021Z</t>
-  </si>
-  <si>
-    <t>TC_4025</t>
-  </si>
-  <si>
-    <t>TC_SEC_002: Unauthorized access prevention to dashboard</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.025Z</t>
-  </si>
-  <si>
-    <t>TC_4029</t>
-  </si>
-  <si>
-    <t>TC_SEC_003: Protected route redirection to login</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.029Z</t>
-  </si>
-  <si>
-    <t>TC_4039</t>
-  </si>
-  <si>
-    <t>TC_SEC_004: Logout invalidates session</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.039Z</t>
-  </si>
-  <si>
-    <t>TC_4042</t>
-  </si>
-  <si>
-    <t>TC_SEC_005: Role-based access control (Admin)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.042Z</t>
-  </si>
-  <si>
-    <t>TC_4050</t>
-  </si>
-  <si>
-    <t>TC_SEC_006: Role-based access control (User)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.050Z</t>
-  </si>
-  <si>
-    <t>TC_4052</t>
-  </si>
-  <si>
-    <t>TC_SEC_007: XSS injection prevention in forms</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.052Z</t>
-  </si>
-  <si>
-    <t>TC_4056</t>
-  </si>
-  <si>
-    <t>TC_SEC_008: SQL injection prevention in search</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.056Z</t>
-  </si>
-  <si>
-    <t>TC_4059</t>
-  </si>
-  <si>
-    <t>TC_SEC_009: CSRF token presence</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.059Z</t>
-  </si>
-  <si>
-    <t>TC_SEC_010: Secure cookie attributes</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:14.072Z</t>
-  </si>
-  <si>
-    <t>TC_5726</t>
-  </si>
-  <si>
-    <t>UI/UX Test</t>
-  </si>
-  <si>
-    <t>TC_UI_001: Core element visibility on load</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.726Z</t>
-  </si>
-  <si>
-    <t>TC_5737</t>
-  </si>
-  <si>
-    <t>TC_UI_002: Button alignment and spacing</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.737Z</t>
-  </si>
-  <si>
-    <t>TC_5740</t>
-  </si>
-  <si>
-    <t>TC_UI_003: Form layout consistency</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.740Z</t>
-  </si>
-  <si>
-    <t>TC_5745</t>
-  </si>
-  <si>
-    <t>TC_UI_004: Responsive layout checks (Mobile viewport)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.745Z</t>
-  </si>
-  <si>
-    <t>TC_5750</t>
-  </si>
-  <si>
-    <t>TC_UI_005: Responsive layout checks (Tablet viewport)</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.750Z</t>
-  </si>
-  <si>
-    <t>TC_5755</t>
-  </si>
-  <si>
-    <t>TC_UI_006: Navigation menu usability</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.755Z</t>
-  </si>
-  <si>
-    <t>TC_5758</t>
-  </si>
-  <si>
-    <t>TC_UI_007: Broken link detection across major pages</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.758Z</t>
-  </si>
-  <si>
-    <t>TC_5761</t>
-  </si>
-  <si>
-    <t>TC_UI_008: Image loading and resolution verification</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.761Z</t>
-  </si>
-  <si>
-    <t>TC_5767</t>
-  </si>
-  <si>
-    <t>TC_UI_009: Font family and typography consistency</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.767Z</t>
-  </si>
-  <si>
-    <t>TC_5772</t>
-  </si>
-  <si>
-    <t>TC_UI_010: Color palette and contrast accessibility</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.772Z</t>
-  </si>
-  <si>
-    <t>TC_5786</t>
-  </si>
-  <si>
-    <t>Unit Testing</t>
-  </si>
-  <si>
-    <t>TC_UNIT_001: Validate password hashing utility logic</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.786Z</t>
-  </si>
-  <si>
-    <t>TC_5789</t>
-  </si>
-  <si>
-    <t>TC_UNIT_002: Validate email regex format utility</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.789Z</t>
-  </si>
-  <si>
-    <t>TC_5792</t>
-  </si>
-  <si>
-    <t>TC_UNIT_003: Validate URL parsing utility</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.792Z</t>
-  </si>
-  <si>
-    <t>TC_5795</t>
-  </si>
-  <si>
-    <t>TC_UNIT_004: Validate date formatting helper</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.795Z</t>
-  </si>
-  <si>
-    <t>TC_5802</t>
-  </si>
-  <si>
-    <t>TC_UNIT_005: Verify number currency formatting helper</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.802Z</t>
-  </si>
-  <si>
-    <t>TC_5805</t>
-  </si>
-  <si>
-    <t>TC_UNIT_006: Check application state reducer for login</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.806Z</t>
-  </si>
-  <si>
-    <t>TC_5809</t>
-  </si>
-  <si>
-    <t>TC_UNIT_007: Check application state reducer for logout</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.809Z</t>
-  </si>
-  <si>
-    <t>TC_5817</t>
-  </si>
-  <si>
     <t>TC_UNIT_008: Validate local storage persistence helper</t>
   </si>
   <si>
-    <t>2026-06-13T04:41:15.817Z</t>
-  </si>
-  <si>
-    <t>TC_5819</t>
+    <t>2026-06-18T05:58:44.147Z</t>
   </si>
   <si>
     <t>TC_UNIT_009: Test mock data generation for dashboard</t>
   </si>
   <si>
-    <t>2026-06-13T04:41:15.819Z</t>
-  </si>
-  <si>
-    <t>TC_5822</t>
-  </si>
-  <si>
     <t>TC_UNIT_010: Validate theme toggler state boolean logic</t>
   </si>
   <si>
-    <t>2026-06-13T04:41:15.822Z</t>
-  </si>
-  <si>
-    <t>TC_5825</t>
+    <t>TC_4148</t>
   </si>
   <si>
     <t>TC_UNIT_011: Test array sorting utility for company list</t>
   </si>
   <si>
-    <t>2026-06-13T04:41:15.825Z</t>
-  </si>
-  <si>
-    <t>TC_5834</t>
+    <t>2026-06-18T05:58:44.148Z</t>
   </si>
   <si>
     <t>TC_UNIT_012: Test pagination offset calculation utility</t>
   </si>
   <si>
-    <t>2026-06-13T04:41:15.834Z</t>
-  </si>
-  <si>
-    <t>TC_5836</t>
-  </si>
-  <si>
     <t>TC_UNIT_013: Verify input sanitization helper (XSS prevention)</t>
   </si>
   <si>
-    <t>2026-06-13T04:41:15.836Z</t>
-  </si>
-  <si>
-    <t>TC_5840</t>
+    <t>TC_4149</t>
   </si>
   <si>
     <t>TC_UNIT_014: Check token decoding function for expiration logic</t>
   </si>
   <si>
-    <t>2026-06-13T04:41:15.840Z</t>
-  </si>
-  <si>
-    <t>TC_5845</t>
+    <t>2026-06-18T05:58:44.149Z</t>
   </si>
   <si>
     <t>TC_UNIT_015: Validate component classNames concatenation utility</t>
-  </si>
-  <si>
-    <t>2026-06-13T04:41:15.845Z</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1757,7 +1546,7 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>231325</v>
+        <v>193476</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
@@ -1792,7 +1581,7 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>98903</v>
+        <v>122402</v>
       </c>
       <c r="I3" t="s">
         <v>23</v>
@@ -1827,7 +1616,7 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>126385</v>
+        <v>80027</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1862,7 +1651,7 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>200717</v>
+        <v>108013</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1897,7 +1686,7 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>277307</v>
+        <v>230809</v>
       </c>
       <c r="I6" t="s">
         <v>32</v>
@@ -1911,31 +1700,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>232304</v>
+      </c>
+      <c r="I7" t="s">
         <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>282318</v>
-      </c>
-      <c r="I7" t="s">
-        <v>35</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -1946,31 +1735,31 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>231006</v>
+      </c>
+      <c r="I8" t="s">
         <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>277623</v>
-      </c>
-      <c r="I8" t="s">
-        <v>38</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -1981,31 +1770,31 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9">
+        <v>299671</v>
+      </c>
+      <c r="I9" t="s">
         <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9">
-        <v>150901</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -2016,31 +1805,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10">
+        <v>224630</v>
+      </c>
+      <c r="I10" t="s">
         <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10">
-        <v>82066</v>
-      </c>
-      <c r="I10" t="s">
-        <v>44</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -2051,31 +1840,31 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11">
+        <v>168554</v>
+      </c>
+      <c r="I11" t="s">
         <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11">
-        <v>259446</v>
-      </c>
-      <c r="I11" t="s">
-        <v>47</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -2086,13 +1875,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -2107,10 +1896,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>84535</v>
+        <v>92138</v>
       </c>
       <c r="I12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -2121,13 +1910,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -2142,10 +1931,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>299637</v>
+        <v>274058</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -2156,13 +1945,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -2177,10 +1966,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>279128</v>
+        <v>175802</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -2191,13 +1980,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -2212,10 +2001,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>210113</v>
+        <v>141675</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -2226,13 +2015,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -2247,10 +2036,10 @@
         <v>17</v>
       </c>
       <c r="H16">
-        <v>111509</v>
+        <v>123063</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -2261,13 +2050,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -2282,10 +2071,10 @@
         <v>17</v>
       </c>
       <c r="H17">
-        <v>113483</v>
+        <v>143886</v>
       </c>
       <c r="I17" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -2296,13 +2085,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -2317,10 +2106,10 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>64343</v>
+        <v>62888</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -2331,13 +2120,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -2352,10 +2141,10 @@
         <v>17</v>
       </c>
       <c r="H19">
-        <v>276555</v>
+        <v>189088</v>
       </c>
       <c r="I19" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -2366,13 +2155,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -2387,10 +2176,10 @@
         <v>17</v>
       </c>
       <c r="H20">
-        <v>294412</v>
+        <v>184931</v>
       </c>
       <c r="I20" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -2401,13 +2190,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -2422,10 +2211,10 @@
         <v>17</v>
       </c>
       <c r="H21">
-        <v>155540</v>
+        <v>65158</v>
       </c>
       <c r="I21" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -2436,13 +2225,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -2457,10 +2246,10 @@
         <v>17</v>
       </c>
       <c r="H22">
-        <v>219091</v>
+        <v>226631</v>
       </c>
       <c r="I22" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -2471,13 +2260,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -2492,10 +2281,10 @@
         <v>17</v>
       </c>
       <c r="H23">
-        <v>66864</v>
+        <v>234763</v>
       </c>
       <c r="I23" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -2506,13 +2295,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -2527,10 +2316,10 @@
         <v>17</v>
       </c>
       <c r="H24">
-        <v>262603</v>
+        <v>194973</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -2541,13 +2330,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -2562,10 +2351,10 @@
         <v>17</v>
       </c>
       <c r="H25">
-        <v>278192</v>
+        <v>250754</v>
       </c>
       <c r="I25" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -2576,13 +2365,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -2597,10 +2386,10 @@
         <v>17</v>
       </c>
       <c r="H26">
-        <v>214474</v>
+        <v>66509</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -2611,13 +2400,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -2632,10 +2421,10 @@
         <v>17</v>
       </c>
       <c r="H27">
-        <v>210971</v>
+        <v>275603</v>
       </c>
       <c r="I27" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -2646,13 +2435,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -2667,10 +2456,10 @@
         <v>17</v>
       </c>
       <c r="H28">
-        <v>214099</v>
+        <v>232568</v>
       </c>
       <c r="I28" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -2681,13 +2470,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -2702,10 +2491,10 @@
         <v>17</v>
       </c>
       <c r="H29">
-        <v>147467</v>
+        <v>145565</v>
       </c>
       <c r="I29" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -2716,13 +2505,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2737,10 +2526,10 @@
         <v>17</v>
       </c>
       <c r="H30">
-        <v>259041</v>
+        <v>101507</v>
       </c>
       <c r="I30" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2751,13 +2540,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -2772,10 +2561,10 @@
         <v>17</v>
       </c>
       <c r="H31">
-        <v>98464</v>
+        <v>135710</v>
       </c>
       <c r="I31" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -2786,13 +2575,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -2807,10 +2596,10 @@
         <v>17</v>
       </c>
       <c r="H32">
-        <v>209040</v>
+        <v>80815</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -2821,13 +2610,13 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -2842,10 +2631,10 @@
         <v>17</v>
       </c>
       <c r="H33">
-        <v>81550</v>
+        <v>158377</v>
       </c>
       <c r="I33" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -2856,13 +2645,13 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -2877,10 +2666,10 @@
         <v>17</v>
       </c>
       <c r="H34">
-        <v>150250</v>
+        <v>97571</v>
       </c>
       <c r="I34" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -2891,13 +2680,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -2912,10 +2701,10 @@
         <v>17</v>
       </c>
       <c r="H35">
-        <v>146069</v>
+        <v>154779</v>
       </c>
       <c r="I35" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -2926,13 +2715,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -2947,10 +2736,10 @@
         <v>17</v>
       </c>
       <c r="H36">
-        <v>163872</v>
+        <v>107545</v>
       </c>
       <c r="I36" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -2961,13 +2750,13 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
@@ -2982,10 +2771,10 @@
         <v>17</v>
       </c>
       <c r="H37">
-        <v>261031</v>
+        <v>100861</v>
       </c>
       <c r="I37" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -2996,13 +2785,13 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
@@ -3017,10 +2806,10 @@
         <v>17</v>
       </c>
       <c r="H38">
-        <v>181131</v>
+        <v>243465</v>
       </c>
       <c r="I38" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
@@ -3031,13 +2820,13 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
@@ -3052,10 +2841,10 @@
         <v>17</v>
       </c>
       <c r="H39">
-        <v>287726</v>
+        <v>260283</v>
       </c>
       <c r="I39" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
@@ -3066,13 +2855,13 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -3087,10 +2876,10 @@
         <v>17</v>
       </c>
       <c r="H40">
-        <v>63100</v>
+        <v>263683</v>
       </c>
       <c r="I40" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
@@ -3101,13 +2890,13 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
         <v>14</v>
@@ -3122,10 +2911,10 @@
         <v>17</v>
       </c>
       <c r="H41">
-        <v>216221</v>
+        <v>196862</v>
       </c>
       <c r="I41" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -3136,13 +2925,13 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
@@ -3157,10 +2946,10 @@
         <v>17</v>
       </c>
       <c r="H42">
-        <v>149910</v>
+        <v>127247</v>
       </c>
       <c r="I42" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -3171,13 +2960,13 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -3192,10 +2981,10 @@
         <v>17</v>
       </c>
       <c r="H43">
-        <v>104800</v>
+        <v>86237</v>
       </c>
       <c r="I43" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -3206,13 +2995,13 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
@@ -3227,10 +3016,10 @@
         <v>17</v>
       </c>
       <c r="H44">
-        <v>156529</v>
+        <v>140868</v>
       </c>
       <c r="I44" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -3241,13 +3030,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -3262,10 +3051,10 @@
         <v>17</v>
       </c>
       <c r="H45">
-        <v>156770</v>
+        <v>74381</v>
       </c>
       <c r="I45" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -3276,13 +3065,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
@@ -3297,10 +3086,10 @@
         <v>17</v>
       </c>
       <c r="H46">
-        <v>258106</v>
+        <v>288428</v>
       </c>
       <c r="I46" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
@@ -3311,13 +3100,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -3332,10 +3121,10 @@
         <v>17</v>
       </c>
       <c r="H47">
-        <v>82890</v>
+        <v>276544</v>
       </c>
       <c r="I47" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
@@ -3346,13 +3135,13 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
@@ -3367,10 +3156,10 @@
         <v>17</v>
       </c>
       <c r="H48">
-        <v>212724</v>
+        <v>79463</v>
       </c>
       <c r="I48" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -3381,13 +3170,13 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
@@ -3402,10 +3191,10 @@
         <v>17</v>
       </c>
       <c r="H49">
-        <v>100512</v>
+        <v>109714</v>
       </c>
       <c r="I49" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="J49" t="s">
         <v>19</v>
@@ -3416,13 +3205,13 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
         <v>14</v>
@@ -3437,10 +3226,10 @@
         <v>17</v>
       </c>
       <c r="H50">
-        <v>271966</v>
+        <v>61042</v>
       </c>
       <c r="I50" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
@@ -3451,13 +3240,13 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
         <v>14</v>
@@ -3472,10 +3261,10 @@
         <v>17</v>
       </c>
       <c r="H51">
-        <v>188753</v>
+        <v>288944</v>
       </c>
       <c r="I51" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
@@ -3486,13 +3275,13 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
@@ -3507,10 +3296,10 @@
         <v>17</v>
       </c>
       <c r="H52">
-        <v>264796</v>
+        <v>215549</v>
       </c>
       <c r="I52" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="J52" t="s">
         <v>19</v>
@@ -3521,13 +3310,13 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
@@ -3542,10 +3331,10 @@
         <v>17</v>
       </c>
       <c r="H53">
-        <v>114739</v>
+        <v>86973</v>
       </c>
       <c r="I53" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="J53" t="s">
         <v>19</v>
@@ -3556,13 +3345,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
@@ -3577,10 +3366,10 @@
         <v>17</v>
       </c>
       <c r="H54">
-        <v>265885</v>
+        <v>89890</v>
       </c>
       <c r="I54" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="J54" t="s">
         <v>19</v>
@@ -3591,13 +3380,13 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="D55" t="s">
         <v>14</v>
@@ -3612,10 +3401,10 @@
         <v>17</v>
       </c>
       <c r="H55">
-        <v>244202</v>
+        <v>105484</v>
       </c>
       <c r="I55" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="J55" t="s">
         <v>19</v>
@@ -3626,13 +3415,13 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
         <v>14</v>
@@ -3647,10 +3436,10 @@
         <v>17</v>
       </c>
       <c r="H56">
-        <v>181940</v>
+        <v>203933</v>
       </c>
       <c r="I56" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="J56" t="s">
         <v>19</v>
@@ -3661,13 +3450,13 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
@@ -3682,10 +3471,10 @@
         <v>17</v>
       </c>
       <c r="H57">
-        <v>259842</v>
+        <v>98835</v>
       </c>
       <c r="I57" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="J57" t="s">
         <v>19</v>
@@ -3696,13 +3485,13 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="D58" t="s">
         <v>14</v>
@@ -3717,10 +3506,10 @@
         <v>17</v>
       </c>
       <c r="H58">
-        <v>271646</v>
+        <v>259417</v>
       </c>
       <c r="I58" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
@@ -3731,13 +3520,13 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
@@ -3752,10 +3541,10 @@
         <v>17</v>
       </c>
       <c r="H59">
-        <v>131338</v>
+        <v>235388</v>
       </c>
       <c r="I59" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="J59" t="s">
         <v>19</v>
@@ -3766,13 +3555,13 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
@@ -3787,10 +3576,10 @@
         <v>17</v>
       </c>
       <c r="H60">
-        <v>122320</v>
+        <v>111039</v>
       </c>
       <c r="I60" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="J60" t="s">
         <v>19</v>
@@ -3801,13 +3590,13 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
@@ -3822,10 +3611,10 @@
         <v>17</v>
       </c>
       <c r="H61">
-        <v>198649</v>
+        <v>118188</v>
       </c>
       <c r="I61" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="J61" t="s">
         <v>19</v>
@@ -3836,13 +3625,13 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -3857,10 +3646,10 @@
         <v>17</v>
       </c>
       <c r="H62">
-        <v>198345</v>
+        <v>167249</v>
       </c>
       <c r="I62" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="J62" t="s">
         <v>19</v>
@@ -3871,13 +3660,13 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
@@ -3892,10 +3681,10 @@
         <v>17</v>
       </c>
       <c r="H63">
-        <v>141934</v>
+        <v>241911</v>
       </c>
       <c r="I63" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="J63" t="s">
         <v>19</v>
@@ -3906,13 +3695,13 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
@@ -3927,10 +3716,10 @@
         <v>17</v>
       </c>
       <c r="H64">
-        <v>198493</v>
+        <v>98735</v>
       </c>
       <c r="I64" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="J64" t="s">
         <v>19</v>
@@ -3941,13 +3730,13 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
@@ -3962,10 +3751,10 @@
         <v>17</v>
       </c>
       <c r="H65">
-        <v>232824</v>
+        <v>227058</v>
       </c>
       <c r="I65" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="J65" t="s">
         <v>19</v>
@@ -3976,13 +3765,13 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
@@ -3997,10 +3786,10 @@
         <v>17</v>
       </c>
       <c r="H66">
-        <v>122343</v>
+        <v>97285</v>
       </c>
       <c r="I66" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="J66" t="s">
         <v>19</v>
@@ -4011,13 +3800,13 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="D67" t="s">
         <v>14</v>
@@ -4032,10 +3821,10 @@
         <v>17</v>
       </c>
       <c r="H67">
-        <v>87657</v>
+        <v>168663</v>
       </c>
       <c r="I67" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="J67" t="s">
         <v>19</v>
@@ -4046,13 +3835,13 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -4067,15 +3856,50 @@
         <v>17</v>
       </c>
       <c r="H68">
-        <v>171955</v>
+        <v>86445</v>
       </c>
       <c r="I68" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="J68" t="s">
         <v>19</v>
       </c>
       <c r="K68" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>177</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" t="s">
+        <v>178</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H69">
+        <v>63415</v>
+      </c>
+      <c r="I69" t="s">
+        <v>179</v>
+      </c>
+      <c r="J69" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4139,13 +3963,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -4154,19 +3978,19 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="H2">
-        <v>203249</v>
+        <v>280673</v>
       </c>
       <c r="I2" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="J2" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="K2" t="s">
         <v>20</v>
@@ -4174,13 +3998,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -4195,10 +4019,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>79050</v>
+        <v>247375</v>
       </c>
       <c r="I3" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -4209,13 +4033,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -4230,10 +4054,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>197037</v>
+        <v>142519</v>
       </c>
       <c r="I4" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -4244,13 +4068,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -4265,10 +4089,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>106284</v>
+        <v>222714</v>
       </c>
       <c r="I5" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -4279,13 +4103,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -4300,10 +4124,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>136944</v>
+        <v>65594</v>
       </c>
       <c r="I6" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -4314,13 +4138,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -4335,10 +4159,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>178617</v>
+        <v>221852</v>
       </c>
       <c r="I7" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -4349,13 +4173,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -4370,10 +4194,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>271177</v>
+        <v>236283</v>
       </c>
       <c r="I8" t="s">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -4442,13 +4266,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -4463,10 +4287,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>226897</v>
+        <v>219281</v>
       </c>
       <c r="I2" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -4477,13 +4301,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -4498,10 +4322,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>260487</v>
+        <v>93057</v>
       </c>
       <c r="I3" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -4512,13 +4336,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -4533,10 +4357,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>130721</v>
+        <v>62980</v>
       </c>
       <c r="I4" t="s">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -4547,13 +4371,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -4568,10 +4392,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>247214</v>
+        <v>148806</v>
       </c>
       <c r="I5" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -4582,13 +4406,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -4603,10 +4427,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>241418</v>
+        <v>236191</v>
       </c>
       <c r="I6" t="s">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -4617,13 +4441,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -4638,10 +4462,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>133419</v>
+        <v>140405</v>
       </c>
       <c r="I7" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -4652,13 +4476,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -4673,10 +4497,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>284836</v>
+        <v>222092</v>
       </c>
       <c r="I8" t="s">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -4687,13 +4511,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -4708,10 +4532,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>239424</v>
+        <v>110395</v>
       </c>
       <c r="I9" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -4722,13 +4546,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -4743,10 +4567,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>269511</v>
+        <v>232702</v>
       </c>
       <c r="I10" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -4757,13 +4581,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -4778,10 +4602,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>185478</v>
+        <v>168864</v>
       </c>
       <c r="I11" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -4792,13 +4616,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -4813,10 +4637,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>244955</v>
+        <v>122200</v>
       </c>
       <c r="I12" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -4827,13 +4651,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -4848,10 +4672,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>242660</v>
+        <v>108687</v>
       </c>
       <c r="I13" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -4862,13 +4686,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="B14" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -4883,10 +4707,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>71708</v>
+        <v>286058</v>
       </c>
       <c r="I14" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -4897,13 +4721,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>239</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -4918,10 +4742,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>207869</v>
+        <v>252718</v>
       </c>
       <c r="I15" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -4932,13 +4756,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="B16" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C16" t="s">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -4953,10 +4777,10 @@
         <v>17</v>
       </c>
       <c r="H16">
-        <v>241028</v>
+        <v>68425</v>
       </c>
       <c r="I16" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -4967,14 +4791,14 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="B17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" t="s">
         <v>244</v>
       </c>
-      <c r="C17" t="s">
-        <v>290</v>
-      </c>
       <c r="D17" t="s">
         <v>14</v>
       </c>
@@ -4988,10 +4812,10 @@
         <v>17</v>
       </c>
       <c r="H17">
-        <v>105070</v>
+        <v>289794</v>
       </c>
       <c r="I17" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -5002,13 +4826,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="B18" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -5023,10 +4847,10 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>196521</v>
+        <v>245096</v>
       </c>
       <c r="I18" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -5037,13 +4861,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>296</v>
+        <v>250</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -5058,10 +4882,10 @@
         <v>17</v>
       </c>
       <c r="H19">
-        <v>109849</v>
+        <v>147894</v>
       </c>
       <c r="I19" t="s">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -5072,13 +4896,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="B20" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C20" t="s">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -5093,10 +4917,10 @@
         <v>17</v>
       </c>
       <c r="H20">
-        <v>101681</v>
+        <v>65125</v>
       </c>
       <c r="I20" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -5107,13 +4931,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C21" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -5128,10 +4952,10 @@
         <v>17</v>
       </c>
       <c r="H21">
-        <v>145593</v>
+        <v>260739</v>
       </c>
       <c r="I21" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -5142,13 +4966,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s">
-        <v>305</v>
+        <v>258</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -5163,10 +4987,10 @@
         <v>17</v>
       </c>
       <c r="H22">
-        <v>80748</v>
+        <v>157411</v>
       </c>
       <c r="I22" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -5177,13 +5001,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C23" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -5198,10 +5022,10 @@
         <v>17</v>
       </c>
       <c r="H23">
-        <v>83978</v>
+        <v>91526</v>
       </c>
       <c r="I23" t="s">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -5212,13 +5036,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C24" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -5233,10 +5057,10 @@
         <v>17</v>
       </c>
       <c r="H24">
-        <v>161282</v>
+        <v>79600</v>
       </c>
       <c r="I24" t="s">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -5247,13 +5071,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C25" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -5268,10 +5092,10 @@
         <v>17</v>
       </c>
       <c r="H25">
-        <v>286595</v>
+        <v>122861</v>
       </c>
       <c r="I25" t="s">
-        <v>315</v>
+        <v>264</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -5282,13 +5106,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>316</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C26" t="s">
-        <v>317</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -5303,10 +5127,10 @@
         <v>17</v>
       </c>
       <c r="H26">
-        <v>283485</v>
+        <v>115885</v>
       </c>
       <c r="I26" t="s">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -5317,13 +5141,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C27" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -5338,10 +5162,10 @@
         <v>17</v>
       </c>
       <c r="H27">
-        <v>293264</v>
+        <v>69326</v>
       </c>
       <c r="I27" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -5352,13 +5176,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>322</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C28" t="s">
-        <v>323</v>
+        <v>273</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -5373,10 +5197,10 @@
         <v>17</v>
       </c>
       <c r="H28">
-        <v>119805</v>
+        <v>163925</v>
       </c>
       <c r="I28" t="s">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -5387,13 +5211,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C29" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -5408,10 +5232,10 @@
         <v>17</v>
       </c>
       <c r="H29">
-        <v>93478</v>
+        <v>240447</v>
       </c>
       <c r="I29" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -5422,13 +5246,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C30" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -5443,10 +5267,10 @@
         <v>17</v>
       </c>
       <c r="H30">
-        <v>99721</v>
+        <v>126672</v>
       </c>
       <c r="I30" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -5457,13 +5281,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C31" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -5478,10 +5302,10 @@
         <v>17</v>
       </c>
       <c r="H31">
-        <v>113669</v>
+        <v>99400</v>
       </c>
       <c r="I31" t="s">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -5492,13 +5316,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>334</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C32" t="s">
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -5513,10 +5337,10 @@
         <v>17</v>
       </c>
       <c r="H32">
-        <v>121826</v>
+        <v>208774</v>
       </c>
       <c r="I32" t="s">
-        <v>336</v>
+        <v>284</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -5527,13 +5351,13 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>337</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C33" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -5548,10 +5372,10 @@
         <v>17</v>
       </c>
       <c r="H33">
-        <v>179910</v>
+        <v>288594</v>
       </c>
       <c r="I33" t="s">
-        <v>339</v>
+        <v>284</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -5562,13 +5386,13 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C34" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -5583,10 +5407,10 @@
         <v>17</v>
       </c>
       <c r="H34">
-        <v>84850</v>
+        <v>68237</v>
       </c>
       <c r="I34" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -5597,13 +5421,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C35" t="s">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -5618,10 +5442,10 @@
         <v>17</v>
       </c>
       <c r="H35">
-        <v>221329</v>
+        <v>141525</v>
       </c>
       <c r="I35" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -5632,13 +5456,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C36" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -5653,10 +5477,10 @@
         <v>17</v>
       </c>
       <c r="H36">
-        <v>121297</v>
+        <v>76962</v>
       </c>
       <c r="I36" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -5672,6 +5496,192 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2">
+        <v>224452</v>
+      </c>
+      <c r="I2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2">
+        <v>71503</v>
+      </c>
+      <c r="I2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -5725,13 +5735,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>348</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -5746,10 +5756,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>204848</v>
+        <v>145359</v>
       </c>
       <c r="I2" t="s">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -5760,13 +5770,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C3" t="s">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -5781,10 +5791,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>230706</v>
+        <v>296756</v>
       </c>
       <c r="I3" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -5795,13 +5805,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="B4" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C4" t="s">
-        <v>356</v>
+        <v>310</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -5816,10 +5826,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>193756</v>
+        <v>97187</v>
       </c>
       <c r="I4" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -5830,13 +5840,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>311</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -5851,10 +5861,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>172467</v>
+        <v>185922</v>
       </c>
       <c r="I5" t="s">
-        <v>360</v>
+        <v>313</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -5865,13 +5875,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>361</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -5886,10 +5896,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>287184</v>
+        <v>67022</v>
       </c>
       <c r="I6" t="s">
-        <v>363</v>
+        <v>313</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -5900,13 +5910,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>364</v>
+        <v>315</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C7" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -5921,10 +5931,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>274969</v>
+        <v>138490</v>
       </c>
       <c r="I7" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -5935,13 +5945,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -5956,10 +5966,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>266711</v>
+        <v>114300</v>
       </c>
       <c r="I8" t="s">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -5970,13 +5980,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>370</v>
+        <v>319</v>
       </c>
       <c r="B9" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C9" t="s">
-        <v>371</v>
+        <v>320</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -5991,10 +6001,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>123535</v>
+        <v>119072</v>
       </c>
       <c r="I9" t="s">
-        <v>372</v>
+        <v>321</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -6005,13 +6015,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="B10" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -6026,10 +6036,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>160317</v>
+        <v>150498</v>
       </c>
       <c r="I10" t="s">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -6040,13 +6050,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>376</v>
+        <v>323</v>
       </c>
       <c r="B11" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C11" t="s">
-        <v>377</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -6061,10 +6071,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>131506</v>
+        <v>221659</v>
       </c>
       <c r="I11" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -6079,7 +6089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -6133,13 +6143,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>379</v>
+        <v>326</v>
       </c>
       <c r="B2" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C2" t="s">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -6154,10 +6164,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>291778</v>
+        <v>247014</v>
       </c>
       <c r="I2" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -6168,13 +6178,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>384</v>
+        <v>330</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -6189,10 +6199,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>100332</v>
+        <v>236121</v>
       </c>
       <c r="I3" t="s">
-        <v>385</v>
+        <v>329</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -6203,13 +6213,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>386</v>
+        <v>326</v>
       </c>
       <c r="B4" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C4" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -6224,10 +6234,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>238128</v>
+        <v>257039</v>
       </c>
       <c r="I4" t="s">
-        <v>388</v>
+        <v>329</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -6238,13 +6248,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C5" t="s">
-        <v>390</v>
+        <v>333</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -6259,10 +6269,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>223002</v>
+        <v>172709</v>
       </c>
       <c r="I5" t="s">
-        <v>391</v>
+        <v>334</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -6273,13 +6283,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>392</v>
+        <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C6" t="s">
-        <v>393</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -6294,10 +6304,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>96183</v>
+        <v>137780</v>
       </c>
       <c r="I6" t="s">
-        <v>394</v>
+        <v>334</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -6308,13 +6318,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="B7" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C7" t="s">
-        <v>396</v>
+        <v>337</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -6329,10 +6339,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>166341</v>
+        <v>115642</v>
       </c>
       <c r="I7" t="s">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -6343,13 +6353,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>398</v>
+        <v>336</v>
       </c>
       <c r="B8" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C8" t="s">
-        <v>399</v>
+        <v>339</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -6364,10 +6374,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>133077</v>
+        <v>255031</v>
       </c>
       <c r="I8" t="s">
-        <v>400</v>
+        <v>338</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -6378,13 +6388,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>401</v>
+        <v>340</v>
       </c>
       <c r="B9" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -6399,10 +6409,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>242962</v>
+        <v>160184</v>
       </c>
       <c r="I9" t="s">
-        <v>403</v>
+        <v>342</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -6413,13 +6423,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>404</v>
+        <v>340</v>
       </c>
       <c r="B10" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -6434,10 +6444,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>241782</v>
+        <v>92180</v>
       </c>
       <c r="I10" t="s">
-        <v>406</v>
+        <v>342</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -6448,13 +6458,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>407</v>
+        <v>340</v>
       </c>
       <c r="B11" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C11" t="s">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -6469,10 +6479,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>212709</v>
+        <v>226882</v>
       </c>
       <c r="I11" t="s">
-        <v>409</v>
+        <v>342</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -6483,13 +6493,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>410</v>
+        <v>345</v>
       </c>
       <c r="B12" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C12" t="s">
-        <v>411</v>
+        <v>346</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -6504,10 +6514,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>238754</v>
+        <v>190210</v>
       </c>
       <c r="I12" t="s">
-        <v>412</v>
+        <v>347</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -6518,13 +6528,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>413</v>
+        <v>345</v>
       </c>
       <c r="B13" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C13" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -6539,10 +6549,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>112153</v>
+        <v>286302</v>
       </c>
       <c r="I13" t="s">
-        <v>415</v>
+        <v>347</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -6553,13 +6563,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>416</v>
+        <v>345</v>
       </c>
       <c r="B14" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C14" t="s">
-        <v>417</v>
+        <v>349</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -6574,10 +6584,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>162850</v>
+        <v>203699</v>
       </c>
       <c r="I14" t="s">
-        <v>418</v>
+        <v>347</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -6588,13 +6598,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>419</v>
+        <v>350</v>
       </c>
       <c r="B15" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C15" t="s">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -6609,10 +6619,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>95700</v>
+        <v>198732</v>
       </c>
       <c r="I15" t="s">
-        <v>421</v>
+        <v>352</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -6623,13 +6633,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>422</v>
+        <v>350</v>
       </c>
       <c r="B16" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C16" t="s">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -6644,10 +6654,10 @@
         <v>17</v>
       </c>
       <c r="H16">
-        <v>66394</v>
+        <v>248812</v>
       </c>
       <c r="I16" t="s">
-        <v>424</v>
+        <v>352</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
